--- a/entertainment_forms/026_film_editor_referral_form--entertainment_forms.xlsx
+++ b/entertainment_forms/026_film_editor_referral_form--entertainment_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -832,12 +832,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>film_editor_referral_form_submitted_time</t>
+          <t>film_editor_referral_form_submitted_time_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Film Editor Referral Form Submitted Time</t>
+          <t>Film Editor Referral Form Submitted Time 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -901,12 +901,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>film_editor_referral_form_submitted</t>
+          <t>film_editor_referral_form_submitted_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Film Editor Referral Form Submitted</t>
+          <t>Film Editor Referral Form Submitted 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>film_editor_form_comments</t>
+          <t>film_editor_form_comments_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Film Editor Form Comments</t>
+          <t>Film Editor Form Comments 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
